--- a/app/data/trisk_portfolio.xlsx
+++ b/app/data/trisk_portfolio.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
+  <si>
+    <t>company_id</t>
+  </si>
   <si>
     <t>company_name</t>
   </si>
@@ -35,9 +38,6 @@
   </si>
   <si>
     <t>loss_given_default</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Automotive</t>
@@ -114,7 +114,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,6 +124,12 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -163,22 +169,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="9">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -186,23 +183,17 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -506,363 +497,310 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
-      <c r="A2" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
-      <c r="A6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
-      <c r="A7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
-      <c r="A8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="E7" s="1"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
-      <c r="A9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="E8" s="1"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
-      <c r="A10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="E9" s="1"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
-      <c r="A11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
-      <c r="A12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
-      <c r="A13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="E12" s="1"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
-      <c r="A14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="E13" s="1"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
-      <c r="A15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="E14" s="1"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
-      <c r="A16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="E15" s="1"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
-      <c r="A17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="5" t="s">
+      <c r="E16" s="1"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
-      <c r="A18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="5" t="s">
+      <c r="E17" s="1"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="6"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
-      <c r="A19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="5" t="s">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="6"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
-      <c r="A20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="5" t="s">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="6"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
